--- a/research/GXH.NZ/Reports/GXH.NZ_DCF_Model.xlsx
+++ b/research/GXH.NZ/Reports/GXH.NZ_DCF_Model.xlsx
@@ -2299,9 +2299,10 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24">
-        <f> Owner FCF pre-NCI</f>
-        <v>0</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>= Owner FCF pre-NCI</t>
+        </is>
       </c>
       <c r="C24" s="6">
         <v>11.887</v>
@@ -2316,9 +2317,10 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="8">
-        <f> Owner FCF post-NCI (to GXH shareholders) - Year 0 base</f>
-        <v>0</v>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>= Owner FCF post-NCI (to GXH shareholders) - Year 0 base</t>
+        </is>
       </c>
       <c r="C26" s="6">
         <v>9.366956</v>
